--- a/src/InsightAiOffice.App/assets/tutorials/sample-outputs/excel_gold.xlsx
+++ b/src/InsightAiOffice.App/assets/tutorials/sample-outputs/excel_gold.xlsx
@@ -6,7 +6,9 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="売上実績" sheetId="1" r:id="rId2"/>
+    <x:sheet name="月次売上サマリー" sheetId="1" r:id="rId2"/>
+    <x:sheet name="部門別実績" sheetId="2" r:id="rId3"/>
+    <x:sheet name="案件一覧" sheetId="3" r:id="rId4"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -16,46 +18,133 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>売上実績</x:t>
+    <x:t>月次売上サマリー</x:t>
   </x:si>
   <x:si>
     <x:t>月</x:t>
   </x:si>
   <x:si>
-    <x:t>部門</x:t>
-  </x:si>
-  <x:si>
-    <x:t>売上金額</x:t>
-  </x:si>
-  <x:si>
-    <x:t>前年同月</x:t>
+    <x:t>売上高（万円）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>原価（万円）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>粗利（万円）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>粗利率</x:t>
+  </x:si>
+  <x:si>
+    <x:t>受注件数</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026年1月</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026年2月</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026年3月</x:t>
+  </x:si>
+  <x:si>
+    <x:t>合計</x:t>
+  </x:si>
+  <x:si>
+    <x:t>部門別実績</x:t>
+  </x:si>
+  <x:si>
+    <x:t>部門名</x:t>
+  </x:si>
+  <x:si>
+    <x:t>目標（万円）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>達成率</x:t>
   </x:si>
   <x:si>
     <x:t>前年比</x:t>
   </x:si>
   <x:si>
-    <x:t>目標</x:t>
-  </x:si>
-  <x:si>
-    <x:t>達成率</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026/01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>東京本社</x:t>
-  </x:si>
-  <x:si>
-    <x:t>大阪支社</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026/02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026/03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>合計</x:t>
+    <x:t>コンサルティング事業部</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ソリューション事業部</x:t>
+  </x:si>
+  <x:si>
+    <x:t>クラウド事業部</x:t>
+  </x:si>
+  <x:si>
+    <x:t>保守サポート事業部</x:t>
+  </x:si>
+  <x:si>
+    <x:t>案件一覧</x:t>
+  </x:si>
+  <x:si>
+    <x:t>案件名</x:t>
+  </x:si>
+  <x:si>
+    <x:t>顧客名</x:t>
+  </x:si>
+  <x:si>
+    <x:t>金額（万円）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ステータス</x:t>
+  </x:si>
+  <x:si>
+    <x:t>担当部門</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DX推進プロジェクト Phase2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A製造株式会社</x:t>
+  </x:si>
+  <x:si>
+    <x:t>進行中</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AI導入支援 本番移行</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B金融株式会社</x:t>
+  </x:si>
+  <x:si>
+    <x:t>受注確定</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基幹システム刷新</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C小売株式会社</x:t>
+  </x:si>
+  <x:si>
+    <x:t>開発準備中</x:t>
+  </x:si>
+  <x:si>
+    <x:t>クラウド移行支援</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D通信株式会社</x:t>
+  </x:si>
+  <x:si>
+    <x:t>デジタル化推進計画</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E市役所</x:t>
+  </x:si>
+  <x:si>
+    <x:t>要件定義中</x:t>
+  </x:si>
+  <x:si>
+    <x:t>セキュリティ強化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F保険株式会社</x:t>
+  </x:si>
+  <x:si>
+    <x:t>提案中</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -255,7 +344,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -284,6 +373,10 @@
       <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -293,6 +386,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="165" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -600,32 +697,30 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
     <x:pageSetUpPr fitToPage="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G10"/>
+  <x:dimension ref="A1:F7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.996339" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="4" width="13.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="4" width="17.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="10.710625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7" ht="30" customHeight="1">
+    <x:row r="1" spans="1:6" ht="30" customHeight="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:7" ht="4" customHeight="1">
+    <x:row r="2" spans="1:6" ht="4" customHeight="1">
       <x:c r="A2" s="2"/>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
       <x:c r="F2" s="2"/>
-      <x:c r="G2" s="2"/>
-    </x:row>
-    <x:row r="3" spans="1:7" ht="28" customHeight="1">
+    </x:row>
+    <x:row r="3" spans="1:6" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -644,172 +739,401 @@
       <x:c r="F3" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="s">
+    </x:row>
+    <x:row r="4" spans="1:6" ht="22" customHeight="1">
+      <x:c r="A4" s="4" t="s">
         <x:v>7</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7" ht="22" customHeight="1">
-      <x:c r="A4" s="4" t="s">
+      <x:c r="B4" s="5">
+        <x:v>108500</x:v>
+      </x:c>
+      <x:c r="C4" s="5">
+        <x:v>72300</x:v>
+      </x:c>
+      <x:c r="D4" s="5">
+        <x:v>36200</x:v>
+      </x:c>
+      <x:c r="E4" s="6">
+        <x:v>33.4</x:v>
+      </x:c>
+      <x:c r="F4" s="7">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:6" ht="22" customHeight="1">
+      <x:c r="A5" s="8" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="s">
+      <x:c r="B5" s="9">
+        <x:v>115200</x:v>
+      </x:c>
+      <x:c r="C5" s="9">
+        <x:v>76800</x:v>
+      </x:c>
+      <x:c r="D5" s="9">
+        <x:v>38400</x:v>
+      </x:c>
+      <x:c r="E5" s="10">
+        <x:v>33.3</x:v>
+      </x:c>
+      <x:c r="F5" s="11">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:6" ht="22" customHeight="1">
+      <x:c r="A6" s="4" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C4" s="5">
-        <x:v>12500000</x:v>
-      </x:c>
-      <x:c r="D4" s="5">
-        <x:v>11000000</x:v>
-      </x:c>
-      <x:c r="E4" s="6">
-        <x:v>13.6</x:v>
-      </x:c>
-      <x:c r="F4" s="5">
-        <x:v>13000000</x:v>
-      </x:c>
-      <x:c r="G4" s="6">
-        <x:v>96.2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7" ht="22" customHeight="1">
-      <x:c r="A5" s="7" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
+      <x:c r="B6" s="5">
+        <x:v>128000</x:v>
+      </x:c>
+      <x:c r="C6" s="5">
+        <x:v>84200</x:v>
+      </x:c>
+      <x:c r="D6" s="5">
+        <x:v>43800</x:v>
+      </x:c>
+      <x:c r="E6" s="6">
+        <x:v>34.2</x:v>
+      </x:c>
+      <x:c r="F6" s="7">
+        <x:v>156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:6" ht="24" customHeight="1">
+      <x:c r="A7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C5" s="8">
-        <x:v>6800000</x:v>
-      </x:c>
-      <x:c r="D5" s="8">
-        <x:v>6500000</x:v>
-      </x:c>
-      <x:c r="E5" s="9">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="F5" s="8">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="G5" s="9">
-        <x:v>97.1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7" ht="22" customHeight="1">
-      <x:c r="A6" s="4" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="5">
-        <x:v>13200000</x:v>
-      </x:c>
-      <x:c r="D6" s="5">
-        <x:v>11500000</x:v>
-      </x:c>
-      <x:c r="E6" s="6">
-        <x:v>14.8</x:v>
-      </x:c>
-      <x:c r="F6" s="5">
-        <x:v>13000000</x:v>
-      </x:c>
-      <x:c r="G6" s="6">
-        <x:v>101.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7" ht="22" customHeight="1">
-      <x:c r="A7" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="8">
-        <x:v>7200000</x:v>
-      </x:c>
-      <x:c r="D7" s="8">
-        <x:v>6800000</x:v>
-      </x:c>
-      <x:c r="E7" s="9">
-        <x:v>5.9</x:v>
-      </x:c>
-      <x:c r="F7" s="8">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="G7" s="9">
-        <x:v>102.9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7" ht="22" customHeight="1">
-      <x:c r="A8" s="4" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B8" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C8" s="5">
-        <x:v>14800000</x:v>
-      </x:c>
-      <x:c r="D8" s="5">
-        <x:v>12000000</x:v>
-      </x:c>
-      <x:c r="E8" s="6">
-        <x:v>23.3</x:v>
-      </x:c>
-      <x:c r="F8" s="5">
-        <x:v>13000000</x:v>
-      </x:c>
-      <x:c r="G8" s="6">
-        <x:v>113.8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:7" ht="22" customHeight="1">
-      <x:c r="A9" s="7" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="8">
-        <x:v>7500000</x:v>
-      </x:c>
-      <x:c r="D9" s="8">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="E9" s="9">
-        <x:v>7.1</x:v>
-      </x:c>
-      <x:c r="F9" s="8">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="G9" s="9">
-        <x:v>107.1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7" ht="24" customHeight="1">
-      <x:c r="A10" s="10" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B10" s="10"/>
-      <x:c r="C10" s="11">
-        <x:v>62000000</x:v>
-      </x:c>
-      <x:c r="D10" s="11">
-        <x:v>54800000</x:v>
-      </x:c>
-      <x:c r="E10" s="11">
-        <x:v>69.3</x:v>
-      </x:c>
-      <x:c r="F10" s="11">
-        <x:v>60000000</x:v>
-      </x:c>
-      <x:c r="G10" s="11">
-        <x:v>618.6</x:v>
+      <x:c r="B7" s="13">
+        <x:v>351700</x:v>
+      </x:c>
+      <x:c r="C7" s="13">
+        <x:v>233300</x:v>
+      </x:c>
+      <x:c r="D7" s="13">
+        <x:v>118400</x:v>
+      </x:c>
+      <x:c r="E7" s="13">
+        <x:v>100.9</x:v>
+      </x:c>
+      <x:c r="F7" s="13">
+        <x:v>446</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
-    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A1:F1"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+    <x:pageSetUpPr fitToPage="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:E8"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="21.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="5" width="10.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:5" ht="30" customHeight="1">
+      <x:c r="A1" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5" ht="4" customHeight="1">
+      <x:c r="A2" s="2"/>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+    </x:row>
+    <x:row r="3" spans="1:5" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5" ht="22" customHeight="1">
+      <x:c r="A4" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="5">
+        <x:v>52000</x:v>
+      </x:c>
+      <x:c r="C4" s="5">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="D4" s="7">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E4" s="7">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5" ht="22" customHeight="1">
+      <x:c r="A5" s="8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B5" s="9">
+        <x:v>41000</x:v>
+      </x:c>
+      <x:c r="C5" s="9">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="D5" s="10">
+        <x:v>97.6</x:v>
+      </x:c>
+      <x:c r="E5" s="10">
+        <x:v>102.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5" ht="22" customHeight="1">
+      <x:c r="A6" s="4" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B6" s="5">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="C6" s="5">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="D6" s="7">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E6" s="6">
+        <x:v>127.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5" ht="22" customHeight="1">
+      <x:c r="A7" s="8" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B7" s="9">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="C7" s="9">
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="D7" s="11">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E7" s="10">
+        <x:v>85.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5" ht="24" customHeight="1">
+      <x:c r="A8" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B8" s="13">
+        <x:v>128000</x:v>
+      </x:c>
+      <x:c r="C8" s="13">
+        <x:v>127000</x:v>
+      </x:c>
+      <x:c r="D8" s="13">
+        <x:v>396.6</x:v>
+      </x:c>
+      <x:c r="E8" s="13">
+        <x:v>429</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells count="1">
+    <x:mergeCell ref="A1:E1"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+    <x:pageSetUpPr fitToPage="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:E10"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.996339" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:5" ht="30" customHeight="1">
+      <x:c r="A1" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5" ht="4" customHeight="1">
+      <x:c r="A2" s="2"/>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+    </x:row>
+    <x:row r="3" spans="1:5" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5" ht="22" customHeight="1">
+      <x:c r="A4" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C4" s="5">
+        <x:v>18500</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5" ht="22" customHeight="1">
+      <x:c r="A5" s="8" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C5" s="9">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5" ht="22" customHeight="1">
+      <x:c r="A6" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C6" s="5">
+        <x:v>24000</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5" ht="22" customHeight="1">
+      <x:c r="A7" s="8" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C7" s="9">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5" ht="22" customHeight="1">
+      <x:c r="A8" s="4" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C8" s="5">
+        <x:v>6200</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5" ht="22" customHeight="1">
+      <x:c r="A9" s="8" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C9" s="9">
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5" ht="24" customHeight="1">
+      <x:c r="A10" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B10" s="12"/>
+      <x:c r="C10" s="13">
+        <x:v>74000</x:v>
+      </x:c>
+      <x:c r="D10" s="12"/>
+      <x:c r="E10" s="12"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells count="1">
+    <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
